--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-en-rapport-avec-la-prevention.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-en-rapport-avec-la-prevention.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Observation - Fr Observation En rapport avec la prévention</t>
+    <t>Observation - Fr En rapport avec la prévention</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -871,6 +871,273 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
+    <t>Observation.performer.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.id</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.url</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.performer.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Observation.performer.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Observation.performer.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Observation.performer.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Observation.performer.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
+  </si>
+  <si>
     <t>Observation.value[x]</t>
   </si>
   <si>
@@ -922,9 +1189,6 @@
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
@@ -1140,29 +1404,7 @@
     <t>Observation.referenceRange.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.referenceRange.modifierExtension</t>
@@ -1753,11 +1995,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AP77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.26171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.44921875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1784,7 +2026,7 @@
     <col min="26" max="26" width="65.48046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -4472,19 +4714,19 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>273</v>
@@ -4495,12 +4737,8 @@
       <c r="M23" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>277</v>
-      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4548,7 +4786,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4557,47 +4795,47 @@
         <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4609,20 +4847,18 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>140</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4646,28 +4882,28 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>283</v>
@@ -4676,13 +4912,13 @@
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -4691,10 +4927,10 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -4705,24 +4941,26 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="D25" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>82</v>
@@ -4731,20 +4969,16 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>286</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4768,11 +5002,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -4790,7 +5026,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4802,33 +5038,33 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4839,10 +5075,10 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
@@ -4851,20 +5087,16 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -4912,19 +5144,19 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -4933,10 +5165,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4947,10 +5179,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4958,10 +5190,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -4973,17 +5205,15 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5008,83 +5238,85 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>321</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5093,20 +5325,16 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5130,11 +5358,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>327</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5152,19 +5382,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>322</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5173,10 +5403,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5187,10 +5417,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5213,17 +5443,15 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>331</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>332</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5272,7 +5500,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5284,33 +5512,33 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>337</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>339</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5321,7 +5549,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5333,17 +5561,15 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>340</v>
+        <v>139</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5380,57 +5606,57 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>339</v>
+        <v>283</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5438,10 +5664,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5453,26 +5679,24 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>349</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>350</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>82</v>
@@ -5514,19 +5738,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>348</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5535,10 +5759,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>356</v>
+        <v>136</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5549,10 +5773,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5575,13 +5799,13 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>358</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>359</v>
+        <v>309</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5590,7 +5814,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>82</v>
@@ -5608,13 +5832,11 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5632,7 +5854,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5644,7 +5866,7 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -5656,7 +5878,7 @@
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>362</v>
+        <v>136</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -5667,21 +5889,23 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="D33" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5696,14 +5920,12 @@
         <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>140</v>
+        <v>316</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5752,7 +5974,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>365</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5776,7 +5998,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5787,46 +6009,42 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>366</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>273</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>368</v>
+        <v>274</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -5874,19 +6092,19 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>370</v>
+        <v>276</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -5898,7 +6116,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>136</v>
+        <v>277</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -5909,10 +6127,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>371</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>371</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5923,7 +6141,7 @@
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>82</v>
@@ -5935,13 +6153,13 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>372</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>373</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>374</v>
+        <v>294</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5980,31 +6198,31 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>371</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6013,10 +6231,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>377</v>
+        <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6027,10 +6245,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>378</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6038,7 +6256,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
@@ -6053,22 +6271,24 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>372</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>379</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6110,19 +6330,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>378</v>
+        <v>306</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6131,10 +6351,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>381</v>
+        <v>136</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6145,10 +6365,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>382</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>382</v>
+        <v>308</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6174,17 +6394,13 @@
         <v>192</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>383</v>
+        <v>309</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
@@ -6208,13 +6424,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6232,7 +6448,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>382</v>
+        <v>313</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6250,13 +6466,13 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>302</v>
+        <v>136</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6267,21 +6483,23 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6293,20 +6511,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>392</v>
+        <v>293</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6330,13 +6544,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>397</v>
+        <v>82</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6354,7 +6568,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>391</v>
+        <v>283</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6366,19 +6580,19 @@
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6389,10 +6603,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>398</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>398</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6415,18 +6629,16 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>399</v>
+        <v>273</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>274</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
+        <v>275</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>402</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6474,7 +6686,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>276</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6486,7 +6698,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6498,7 +6710,7 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>403</v>
+        <v>277</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6509,10 +6721,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6523,7 +6735,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6535,13 +6747,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>358</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>405</v>
+        <v>293</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>406</v>
+        <v>294</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6580,31 +6792,31 @@
         <v>82</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>82</v>
+        <v>281</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>283</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6613,10 +6825,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6627,10 +6839,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>408</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6638,10 +6850,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6650,19 +6862,19 @@
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>409</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>410</v>
+        <v>303</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>411</v>
+        <v>304</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>412</v>
+        <v>305</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6670,7 +6882,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>82</v>
+        <v>322</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>82</v>
@@ -6712,19 +6924,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>408</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -6733,10 +6945,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>414</v>
+        <v>136</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6747,10 +6959,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6761,7 +6973,7 @@
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -6770,20 +6982,18 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>416</v>
+        <v>264</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>417</v>
+        <v>309</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6832,13 +7042,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>415</v>
+        <v>313</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -6853,10 +7063,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>420</v>
+        <v>136</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6867,10 +7077,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6878,10 +7088,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6890,29 +7100,27 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>349</v>
+        <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>422</v>
+        <v>303</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>423</v>
+        <v>304</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -6954,19 +7162,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>306</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -6975,10 +7183,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>427</v>
+        <v>136</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6989,10 +7197,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7003,7 +7211,7 @@
         <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7015,13 +7223,13 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>309</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7072,7 +7280,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>361</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7084,7 +7292,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7096,7 +7304,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>362</v>
+        <v>136</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7107,21 +7315,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7130,19 +7338,19 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>273</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>140</v>
+        <v>334</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>142</v>
+        <v>336</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7192,19 +7400,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7216,7 +7424,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>362</v>
+        <v>136</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7227,46 +7435,44 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>430</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>430</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>368</v>
+        <v>340</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7290,13 +7496,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7314,19 +7520,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7349,10 +7555,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>431</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7360,7 +7566,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -7375,20 +7581,18 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>432</v>
+        <v>348</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>433</v>
+        <v>349</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7412,13 +7616,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7436,10 +7640,10 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>431</v>
+        <v>351</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>93</v>
@@ -7454,16 +7658,16 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>214</v>
+        <v>352</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7471,10 +7675,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>353</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>353</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7497,20 +7701,18 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>437</v>
+        <v>273</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>438</v>
+        <v>354</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>275</v>
+        <v>355</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7558,7 +7760,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>357</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7576,27 +7778,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>281</v>
+        <v>136</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>282</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>441</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>441</v>
+        <v>358</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7604,34 +7806,34 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>359</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>442</v>
+        <v>360</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>443</v>
+        <v>361</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>444</v>
+        <v>362</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>287</v>
+        <v>363</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7656,13 +7858,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>288</v>
+        <v>82</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7680,7 +7882,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>441</v>
+        <v>358</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7689,7 +7891,7 @@
         <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>291</v>
+        <v>364</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>105</v>
@@ -7698,38 +7900,38 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>136</v>
+        <v>366</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>292</v>
+        <v>367</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>369</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7744,16 +7946,16 @@
         <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>446</v>
+        <v>370</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>296</v>
+        <v>371</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>297</v>
+        <v>372</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>298</v>
+        <v>373</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7778,13 +7980,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>447</v>
+        <v>374</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>448</v>
+        <v>375</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -7802,16 +8004,16 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>445</v>
+        <v>369</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>105</v>
@@ -7820,41 +8022,41 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>301</v>
+        <v>136</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>302</v>
+        <v>377</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
@@ -7863,19 +8065,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>381</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>352</v>
+        <v>382</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>353</v>
+        <v>383</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7900,13 +8102,11 @@
         <v>82</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -7924,7 +8124,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>378</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7942,23 +8142,3157 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>356</v>
+        <v>387</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP51" t="s" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Y54" s="2"/>
+      <c r="Z54" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP51">
+  <autoFilter ref="A1:AP77">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7968,7 +11302,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI50">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-en-rapport-avec-la-prevention.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-en-rapport-avec-la-prevention.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
